--- a/17 18 20/5.Power Bi/5) Dax/3.DATE/DATE.xlsx
+++ b/17 18 20/5.Power Bi/5) Dax/3.DATE/DATE.xlsx
@@ -62,7 +62,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -343,8 +343,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -356,204 +359,223 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46023</v>
+        <v>46142</v>
       </c>
       <c r="B2" s="1">
-        <f ca="1">A2+RANDBETWEEN(10,100)</f>
-        <v>46099</v>
+        <f>A2+1</f>
+        <v>46143</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <f>A2+20</f>
-        <v>46043</v>
+        <v>46387</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B16" ca="1" si="0">A3+RANDBETWEEN(10,100)</f>
-        <v>46134</v>
+        <f>A3+1</f>
+        <v>46388</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A21" si="1">A3+20</f>
-        <v>46063</v>
+        <v>46023</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>46089</v>
+        <f ca="1">A4+RANDBETWEEN(10,100)</f>
+        <v>46091</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" si="1"/>
-        <v>46083</v>
+        <f>A4+20</f>
+        <v>46043</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>46163</v>
+        <f t="shared" ref="B5:B18" ca="1" si="0">A5+RANDBETWEEN(10,100)</f>
+        <v>46084</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="1"/>
-        <v>46103</v>
+        <f t="shared" ref="A6:A23" si="1">A5+20</f>
+        <v>46063</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46119</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="1"/>
-        <v>46123</v>
+        <v>46083</v>
       </c>
       <c r="B7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46210</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="1"/>
-        <v>46143</v>
+        <v>46103</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46192</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="1"/>
-        <v>46163</v>
+        <v>46123</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46194</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="1"/>
-        <v>46183</v>
+        <v>46143</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46194</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="1"/>
-        <v>46203</v>
+        <v>46163</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46296</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46183</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46245</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="1"/>
-        <v>46243</v>
+        <v>46203</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46325</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="1"/>
-        <v>46263</v>
+        <v>46223</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46273</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="1"/>
-        <v>46283</v>
+        <v>46243</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46322</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
-        <v>46303</v>
+        <v>46263</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>46380</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
-        <v>46323</v>
+        <v>46283</v>
       </c>
       <c r="B17" s="1">
-        <f ca="1">A17+RANDBETWEEN(365,1000)</f>
-        <v>46948</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46336</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
-        <v>46343</v>
+        <v>46303</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" ref="B18:B21" ca="1" si="2">A18+RANDBETWEEN(365,1000)</f>
-        <v>47024</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46351</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
-        <v>46363</v>
+        <v>46323</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>47198</v>
+        <f ca="1">A19+RANDBETWEEN(365,1000)</f>
+        <v>46859</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
-        <v>46383</v>
+        <v>46343</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" ca="1" si="2"/>
-        <v>47328</v>
+        <f t="shared" ref="B20:B23" ca="1" si="2">A20+RANDBETWEEN(365,1000)</f>
+        <v>47305</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
-        <v>46403</v>
+        <v>46363</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>47171</v>
+        <v>46922</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="1"/>
+        <v>46383</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>47027</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="1"/>
+        <v>46403</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" ca="1" si="2"/>
+        <v>47168</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>